--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,45 +1134,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56220022</v>
+        <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>91909</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stamtjärn, Jmt</t>
+          <t>Nybränttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544464</v>
+        <v>544391</v>
       </c>
       <c r="R6" t="n">
-        <v>7010553</v>
+        <v>7010416</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-11-11</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-11-11</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,12 +1219,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1234,13 +1234,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56220022</t>
+          <t>https://artportalen.se/Sighting/137166080</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61667797</v>
+        <v>56220022</v>
       </c>
       <c r="B7" t="n">
         <v>91909</v>
@@ -1271,14 +1271,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mellan Nybräntberget och Överammer, Jmt</t>
+          <t>Stamtjärn, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544361</v>
+        <v>544464</v>
       </c>
       <c r="R7" t="n">
-        <v>7010411</v>
+        <v>7010553</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2014-11-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2014-11-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,34 +1321,16 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1358,16 +1340,16 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61667797</t>
+          <t>https://artportalen.se/Sighting/56220022</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103998271</v>
+        <v>61667797</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,34 +1357,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nybränttjärnen, Jmt</t>
+          <t>Mellan Nybräntberget och Överammer, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544487</v>
+        <v>544361</v>
       </c>
       <c r="R8" t="n">
-        <v>7010407</v>
+        <v>7010411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,22 +1411,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>08:42</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>08:42</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,61 +1428,74 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103998271</t>
+          <t>https://artportalen.se/Sighting/61667797</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103998206</v>
+        <v>103998271</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1520,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544441</v>
+        <v>544487</v>
       </c>
       <c r="R9" t="n">
-        <v>7010395</v>
+        <v>7010407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,11 +1561,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -1605,13 +1585,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103998206</t>
+          <t>https://artportalen.se/Sighting/103998271</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126728410</v>
+        <v>103998206</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1642,14 +1622,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stamtjärnen, S, Jmt</t>
+          <t>Nybränttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544477</v>
+        <v>544441</v>
       </c>
       <c r="R10" t="n">
-        <v>7010541</v>
+        <v>7010395</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,12 +1656,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,66 +1682,80 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126728410</t>
+          <t>https://artportalen.se/Sighting/103998206</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103998385</v>
+        <v>126728410</v>
       </c>
       <c r="B11" t="n">
-        <v>83290</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nybränttjärnen, Jmt</t>
+          <t>Stamtjärnen, S, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544507</v>
+        <v>544477</v>
       </c>
       <c r="R11" t="n">
-        <v>7010430</v>
+        <v>7010541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,22 +1782,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:03</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:03</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,62 +1798,53 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103998385</t>
+          <t>https://artportalen.se/Sighting/126728410</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103998289</v>
+        <v>103998385</v>
       </c>
       <c r="B12" t="n">
-        <v>83307</v>
+        <v>83290</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1869,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544536</v>
+        <v>544507</v>
       </c>
       <c r="R12" t="n">
-        <v>7010445</v>
+        <v>7010430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,16 +1934,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103998289</t>
+          <t>https://artportalen.se/Sighting/103998385</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126728412</v>
+        <v>103998289</v>
       </c>
       <c r="B13" t="n">
-        <v>80432</v>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,34 +1951,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stamtjärnen, S, Jmt</t>
+          <t>Nybränttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544477</v>
+        <v>544536</v>
       </c>
       <c r="R13" t="n">
-        <v>7010541</v>
+        <v>7010445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,12 +2005,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,28 +2031,37 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126728412</t>
+          <t>https://artportalen.se/Sighting/103998289</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126728417</v>
+        <v>126728412</v>
       </c>
       <c r="B14" t="n">
         <v>80432</v>
@@ -2092,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544496</v>
+        <v>544477</v>
       </c>
       <c r="R14" t="n">
-        <v>7010550</v>
+        <v>7010541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2153,38 +2157,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126728417</t>
+          <t>https://artportalen.se/Sighting/126728412</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126728411</v>
+        <v>126728417</v>
       </c>
       <c r="B15" t="n">
-        <v>80468</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2194,10 +2198,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544477</v>
+        <v>544496</v>
       </c>
       <c r="R15" t="n">
-        <v>7010541</v>
+        <v>7010550</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,13 +2259,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126728411</t>
+          <t>https://artportalen.se/Sighting/126728417</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126728416</v>
+        <v>126728411</v>
       </c>
       <c r="B16" t="n">
         <v>80468</v>
@@ -2296,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544496</v>
+        <v>544477</v>
       </c>
       <c r="R16" t="n">
-        <v>7010550</v>
+        <v>7010541</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,16 +2361,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126728416</t>
+          <t>https://artportalen.se/Sighting/126728411</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103998381</v>
+        <v>126728416</v>
       </c>
       <c r="B17" t="n">
-        <v>99017</v>
+        <v>80468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,34 +2378,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219795</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nybränttjärnen, Jmt</t>
+          <t>Stamtjärnen, S, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544462</v>
+        <v>544496</v>
       </c>
       <c r="R17" t="n">
-        <v>7010501</v>
+        <v>7010550</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,22 +2432,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:08</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:08</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,40 +2448,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103998381</t>
+          <t>https://artportalen.se/Sighting/126728416</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103998415</v>
+        <v>103998381</v>
       </c>
       <c r="B18" t="n">
-        <v>99456</v>
+        <v>99017</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,21 +2480,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219880</v>
+        <v>219795</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2519,10 +2504,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544505</v>
+        <v>544462</v>
       </c>
       <c r="R18" t="n">
-        <v>7010373</v>
+        <v>7010501</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,7 +2539,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2564,7 +2549,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,51 +2584,51 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103998415</t>
+          <t>https://artportalen.se/Sighting/103998381</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126728420</v>
+        <v>103998415</v>
       </c>
       <c r="B19" t="n">
-        <v>99118</v>
+        <v>99456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stamtjärnen, S, Jmt</t>
+          <t>Nybränttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544524</v>
+        <v>544505</v>
       </c>
       <c r="R19" t="n">
-        <v>7010558</v>
+        <v>7010373</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,12 +2655,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,28 +2681,37 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126728420</t>
+          <t>https://artportalen.se/Sighting/103998415</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126728438</v>
+        <v>126728420</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2742,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544548</v>
+        <v>544524</v>
       </c>
       <c r="R20" t="n">
-        <v>7010560</v>
+        <v>7010558</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,51 +2807,51 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126728438</t>
+          <t>https://artportalen.se/Sighting/126728420</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103998382</v>
+        <v>126728438</v>
       </c>
       <c r="B21" t="n">
-        <v>103683</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222002</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nybränttjärnen, Jmt</t>
+          <t>Stamtjärnen, S, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544446</v>
+        <v>544548</v>
       </c>
       <c r="R21" t="n">
-        <v>7010552</v>
+        <v>7010560</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2874,22 +2878,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:12</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:12</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,40 +2894,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103998382</t>
+          <t>https://artportalen.se/Sighting/126728438</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>56220024</v>
+        <v>103998382</v>
       </c>
       <c r="B22" t="n">
-        <v>104628</v>
+        <v>103683</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,16 +2926,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2961,14 +2946,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stamtjärn, Jmt</t>
+          <t>Nybränttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544510</v>
+        <v>544446</v>
       </c>
       <c r="R22" t="n">
-        <v>7010555</v>
+        <v>7010552</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2995,12 +2980,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2014-11-11</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2014-11-11</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3011,32 +3006,37 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56220024</t>
+          <t>https://artportalen.se/Sighting/103998382</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103998307</v>
+        <v>56220024</v>
       </c>
       <c r="B23" t="n">
         <v>104628</v>
@@ -3067,14 +3067,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nybränttjärnen, Jmt</t>
+          <t>Stamtjärn, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544451</v>
+        <v>544510</v>
       </c>
       <c r="R23" t="n">
-        <v>7010517</v>
+        <v>7010555</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3101,22 +3101,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:10</t>
+          <t>2014-11-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:10</t>
+          <t>2014-11-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,37 +3117,32 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103998307</t>
+          <t>https://artportalen.se/Sighting/56220024</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103998333</v>
+        <v>103998307</v>
       </c>
       <c r="B24" t="n">
         <v>104628</v>
@@ -3192,10 +3177,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544509</v>
+        <v>544451</v>
       </c>
       <c r="R24" t="n">
-        <v>7010385</v>
+        <v>7010517</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3227,7 +3212,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3222,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3272,16 +3257,16 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103998333</t>
+          <t>https://artportalen.se/Sighting/103998307</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126728422</v>
+        <v>103998333</v>
       </c>
       <c r="B25" t="n">
-        <v>100888</v>
+        <v>104628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,16 +3274,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222584</v>
+        <v>222412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3307,20 +3292,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stamtjärnen, S, Jmt</t>
+          <t>Nybränttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544524</v>
+        <v>544509</v>
       </c>
       <c r="R25" t="n">
-        <v>7010558</v>
+        <v>7010385</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3347,12 +3328,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3361,23 +3352,138 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998333</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126728422</v>
+      </c>
+      <c r="B26" t="n">
+        <v>100888</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stamtjärnen, S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>544524</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7010558</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr">
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126728422</t>
         </is>
@@ -3409,6 +3515,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99278</v>
+        <v>99280</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99280</v>
+        <v>99282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99282</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99297</v>
+        <v>99300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99300</v>
+        <v>99310</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99310</v>
+        <v>99311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99311</v>
+        <v>99316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99316</v>
+        <v>99318</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99324</v>
+        <v>99336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99336</v>
+        <v>99337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99337</v>
+        <v>99340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137166080</v>
       </c>
       <c r="B6" t="n">
-        <v>99340</v>
+        <v>99344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
